--- a/dictionary/variables_master.xlsx
+++ b/dictionary/variables_master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eafit-my.sharepoint.com/personal/rszapatav_eafit_edu_co/Documents/CIAT/Metodología Evaluaciones/surveyProcessingMethodology/dictionary/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="867" documentId="8_{4C1B0862-69B3-42BC-8750-06EDE6596D4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2749BBE-4230-4957-99E1-5B6890D05A4B}"/>
+  <xr:revisionPtr revIDLastSave="891" documentId="8_{4C1B0862-69B3-42BC-8750-06EDE6596D4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2198CE4-74E4-4C57-A05D-2C02807DFB34}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D5E2868F-FAC0-444C-BFCE-6871238D4C9E}"/>
+    <workbookView xWindow="-28920" yWindow="-4725" windowWidth="29040" windowHeight="15720" xr2:uid="{D5E2868F-FAC0-444C-BFCE-6871238D4C9E}"/>
   </bookViews>
   <sheets>
     <sheet name="variables_master" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="216">
   <si>
     <t>variable_name</t>
   </si>
@@ -664,6 +664,24 @@
   </si>
   <si>
     <t>var_type</t>
+  </si>
+  <si>
+    <t>baseline</t>
+  </si>
+  <si>
+    <t>endline</t>
+  </si>
+  <si>
+    <t>plots</t>
+  </si>
+  <si>
+    <t>grouping_var</t>
+  </si>
+  <si>
+    <t>logarithm</t>
+  </si>
+  <si>
+    <t>model_var</t>
   </si>
 </sst>
 </file>
@@ -830,7 +848,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1018,25 +1036,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0070C0"/>
+        <fgColor theme="1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1201,27 +1237,36 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1599,7 +1644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B98D0170-56BF-40AD-B5DE-47C0DB191985}">
-  <dimension ref="A1:V28"/>
+  <dimension ref="A1:AB28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" customWidth="1"/>
@@ -1623,77 +1668,97 @@
     <col min="20" max="20" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="19" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="F1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="8" t="s">
         <v>8</v>
       </c>
       <c r="V1" s="9" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W1" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="X1" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="Y1" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="Z1" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="AA1" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB1" s="12" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>159</v>
       </c>
@@ -1715,7 +1780,7 @@
       <c r="G2">
         <v>1</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="3" t="s">
         <v>160</v>
       </c>
       <c r="K2">
@@ -1727,8 +1792,26 @@
       <c r="V2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>159</v>
       </c>
@@ -1762,8 +1845,26 @@
       <c r="V3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>159</v>
       </c>
@@ -1803,8 +1904,26 @@
       <c r="V4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>159</v>
       </c>
@@ -1841,8 +1960,26 @@
       <c r="V5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>159</v>
       </c>
@@ -1882,8 +2019,26 @@
       <c r="V6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1935,8 +2090,26 @@
       <c r="V7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1979,8 +2152,26 @@
       <c r="V8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -2032,8 +2223,26 @@
       <c r="V9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -2085,8 +2294,26 @@
       <c r="V10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -2126,8 +2353,26 @@
       <c r="V11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -2176,15 +2421,33 @@
       <c r="V12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
       <c r="B13" t="s">
         <v>166</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="3" t="s">
         <v>195</v>
       </c>
       <c r="D13" t="s">
@@ -2205,8 +2468,8 @@
       <c r="K13">
         <v>1</v>
       </c>
-      <c r="L13" s="5"/>
-      <c r="O13" s="5" t="s">
+      <c r="L13" s="3"/>
+      <c r="O13" s="3" t="s">
         <v>197</v>
       </c>
       <c r="P13" t="s">
@@ -2218,8 +2481,26 @@
       <c r="V13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -2265,8 +2546,26 @@
       <c r="V14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -2309,8 +2608,26 @@
       <c r="V15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -2338,7 +2655,7 @@
       <c r="K16">
         <v>1</v>
       </c>
-      <c r="L16" s="5" t="s">
+      <c r="L16" s="3" t="s">
         <v>135</v>
       </c>
       <c r="M16" t="s">
@@ -2365,8 +2682,26 @@
       <c r="V16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -2394,7 +2729,7 @@
       <c r="K17">
         <v>1</v>
       </c>
-      <c r="L17" s="5"/>
+      <c r="L17" s="3"/>
       <c r="O17" t="s">
         <v>138</v>
       </c>
@@ -2416,8 +2751,26 @@
       <c r="V17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -2445,7 +2798,7 @@
       <c r="K18">
         <v>1</v>
       </c>
-      <c r="L18" s="5"/>
+      <c r="L18" s="3"/>
       <c r="O18" t="s">
         <v>139</v>
       </c>
@@ -2467,8 +2820,26 @@
       <c r="V18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -2496,7 +2867,7 @@
       <c r="K19">
         <v>1</v>
       </c>
-      <c r="M19" s="5" t="s">
+      <c r="M19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N19" t="s">
@@ -2520,8 +2891,26 @@
       <c r="V19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -2549,7 +2938,7 @@
       <c r="K20">
         <v>1</v>
       </c>
-      <c r="L20" s="5"/>
+      <c r="L20" s="3"/>
       <c r="M20" t="s">
         <v>148</v>
       </c>
@@ -2574,8 +2963,26 @@
       <c r="V20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -2615,24 +3022,42 @@
       <c r="V21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>173</v>
       </c>
       <c r="B22" t="s">
         <v>174</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="3" t="s">
         <v>184</v>
       </c>
       <c r="D22" t="s">
         <v>207</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="3" t="s">
         <v>185</v>
       </c>
       <c r="G22">
@@ -2659,15 +3084,33 @@
       <c r="V22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>173</v>
       </c>
       <c r="B23" t="s">
         <v>174</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="3" t="s">
         <v>172</v>
       </c>
       <c r="D23" t="s">
@@ -2697,15 +3140,33 @@
       <c r="V23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>173</v>
       </c>
       <c r="B24" t="s">
         <v>175</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D24" t="s">
@@ -2738,24 +3199,42 @@
       <c r="V24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>173</v>
       </c>
       <c r="B25" t="s">
         <v>175</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="3" t="s">
         <v>182</v>
       </c>
       <c r="D25" t="s">
         <v>207</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="3" t="s">
         <v>192</v>
       </c>
       <c r="G25">
@@ -2767,7 +3246,7 @@
       <c r="K25">
         <v>1</v>
       </c>
-      <c r="M25" s="5" t="s">
+      <c r="M25" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N25" t="s">
@@ -2791,24 +3270,42 @@
       <c r="V25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>173</v>
       </c>
       <c r="B26" t="s">
         <v>176</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="5" t="s">
         <v>183</v>
       </c>
       <c r="D26" t="s">
         <v>207</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="3" t="s">
         <v>187</v>
       </c>
       <c r="G26">
@@ -2820,7 +3317,7 @@
       <c r="K26">
         <v>1</v>
       </c>
-      <c r="M26" s="5" t="s">
+      <c r="M26" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O26" t="s">
@@ -2841,8 +3338,26 @@
       <c r="V26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>173</v>
       </c>
@@ -2870,7 +3385,7 @@
       <c r="K27">
         <v>1</v>
       </c>
-      <c r="L27" s="7" t="s">
+      <c r="L27" s="5" t="s">
         <v>189</v>
       </c>
       <c r="N27" t="s">
@@ -2885,8 +3400,26 @@
       <c r="V27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>155</v>
       </c>
@@ -2927,6 +3460,24 @@
         <v>3</v>
       </c>
       <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
         <v>0</v>
       </c>
     </row>
@@ -3159,10 +3710,10 @@
       <c r="B11" t="s">
         <v>155</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="4">
         <v>10</v>
       </c>
-      <c r="D11" s="6"/>
+      <c r="D11" s="4"/>
       <c r="E11" t="s">
         <v>163</v>
       </c>
@@ -3479,10 +4030,10 @@
       <c r="B25" t="s">
         <v>155</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="4">
         <v>14</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="4">
         <v>10</v>
       </c>
       <c r="E25" t="s">

--- a/dictionary/variables_master.xlsx
+++ b/dictionary/variables_master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eafit-my.sharepoint.com/personal/rszapatav_eafit_edu_co/Documents/CIAT/Metodología Evaluaciones/surveyProcessingMethodology/dictionary/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="891" documentId="8_{4C1B0862-69B3-42BC-8750-06EDE6596D4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2198CE4-74E4-4C57-A05D-2C02807DFB34}"/>
+  <xr:revisionPtr revIDLastSave="904" documentId="8_{4C1B0862-69B3-42BC-8750-06EDE6596D4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71673B79-A3F3-41A9-A8FE-5CA76434128A}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-4725" windowWidth="29040" windowHeight="15720" xr2:uid="{D5E2868F-FAC0-444C-BFCE-6871238D4C9E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D5E2868F-FAC0-444C-BFCE-6871238D4C9E}"/>
   </bookViews>
   <sheets>
     <sheet name="variables_master" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="218">
   <si>
     <t>variable_name</t>
   </si>
@@ -675,13 +675,19 @@
     <t>plots</t>
   </si>
   <si>
-    <t>grouping_var</t>
-  </si>
-  <si>
-    <t>logarithm</t>
-  </si>
-  <si>
-    <t>model_var</t>
+    <t>outcome_var</t>
+  </si>
+  <si>
+    <t>control_var</t>
+  </si>
+  <si>
+    <t>logarithm_var</t>
+  </si>
+  <si>
+    <t>fe_var</t>
+  </si>
+  <si>
+    <t>cluster_var</t>
   </si>
 </sst>
 </file>
@@ -1644,7 +1650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B98D0170-56BF-40AD-B5DE-47C0DB191985}">
-  <dimension ref="A1:AB28"/>
+  <dimension ref="A1:AD28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" customWidth="1"/>
@@ -1668,11 +1674,14 @@
     <col min="20" max="20" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="19" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.42578125" customWidth="1"/>
+    <col min="30" max="30" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>3</v>
       </c>
@@ -1748,17 +1757,23 @@
       <c r="Y1" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="Z1" s="11" t="s">
+      <c r="Z1" s="12" t="s">
         <v>213</v>
       </c>
       <c r="AA1" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="AB1" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="AB1" s="12" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC1" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="AD1" s="12" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>159</v>
       </c>
@@ -1810,8 +1825,14 @@
       <c r="AB2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>159</v>
       </c>
@@ -1863,8 +1884,14 @@
       <c r="AB3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>159</v>
       </c>
@@ -1922,8 +1949,14 @@
       <c r="AB4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>159</v>
       </c>
@@ -1978,8 +2011,14 @@
       <c r="AB5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>159</v>
       </c>
@@ -2037,8 +2076,14 @@
       <c r="AB6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -2108,8 +2153,14 @@
       <c r="AB7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -2170,8 +2221,14 @@
       <c r="AB8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -2241,8 +2298,14 @@
       <c r="AB9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -2312,8 +2375,14 @@
       <c r="AB10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -2371,8 +2440,14 @@
       <c r="AB11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -2439,8 +2514,14 @@
       <c r="AB12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -2499,8 +2580,14 @@
       <c r="AB13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -2564,8 +2651,14 @@
       <c r="AB14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -2626,8 +2719,14 @@
       <c r="AB15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -2700,8 +2799,14 @@
       <c r="AB16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -2769,8 +2874,14 @@
       <c r="AB17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -2838,8 +2949,14 @@
       <c r="AB18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -2909,8 +3026,14 @@
       <c r="AB19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -2981,8 +3104,14 @@
       <c r="AB20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -3040,8 +3169,14 @@
       <c r="AB21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>173</v>
       </c>
@@ -3102,8 +3237,14 @@
       <c r="AB22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>173</v>
       </c>
@@ -3158,8 +3299,14 @@
       <c r="AB23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>173</v>
       </c>
@@ -3217,8 +3364,14 @@
       <c r="AB24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>173</v>
       </c>
@@ -3288,8 +3441,14 @@
       <c r="AB25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>173</v>
       </c>
@@ -3356,8 +3515,14 @@
       <c r="AB26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>173</v>
       </c>
@@ -3418,8 +3583,14 @@
       <c r="AB27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>155</v>
       </c>
@@ -3478,6 +3649,12 @@
         <v>0</v>
       </c>
       <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
         <v>0</v>
       </c>
     </row>
